--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
-    <t xml:space="preserve">Learning Resource</t>
+    <t xml:space="preserve">Learning Resources</t>
   </si>
   <si>
     <t xml:space="preserve">(6-3)</t>
@@ -135,18 +135,21 @@
     <t xml:space="preserve">Hamm</t>
   </si>
   <si>
+    <t xml:space="preserve">12/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorn</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">5/21/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zorn</t>
-  </si>
-  <si>
     <t xml:space="preserve">3/23/2026</t>
   </si>
   <si>
@@ -168,7 +171,7 @@
     <t xml:space="preserve">25-180</t>
   </si>
   <si>
-    <t xml:space="preserve">Dynamic Physical Therapy</t>
+    <t xml:space="preserve">Dynamic PT</t>
   </si>
   <si>
     <t xml:space="preserve">12/8/2025</t>
@@ -327,7 +330,7 @@
     <t xml:space="preserve">Enbridge</t>
   </si>
   <si>
-    <t xml:space="preserve">Hain Celestial Group</t>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor; Thomas</t>
@@ -1151,10 +1154,10 @@
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -1162,7 +1165,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -1171,16 +1174,16 @@
         <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1188,7 +1191,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
@@ -1197,16 +1200,16 @@
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -1248,19 +1251,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -1274,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -1294,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -1314,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
@@ -1334,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1348,33 +1351,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>15423</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1383,58 +1386,58 @@
         <v>9430</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
         <v>7928</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>7868</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1448,47 +1451,47 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="n">
         <v>7218</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
         <v>6882</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -1497,13 +1500,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
         <v>6830</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
@@ -1512,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="n">
@@ -1522,47 +1525,47 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>6695</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
         <v>6515</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -1571,7 +1574,7 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
         <v>6461</v>
@@ -1582,62 +1585,62 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
         <v>6431</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
         <v>5440</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" t="n">
         <v>5129</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -1646,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="n">
@@ -1656,7 +1659,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -1665,24 +1668,24 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" t="n">
         <v>4547</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
         <v>33</v>
@@ -1691,12 +1694,12 @@
         <v>4426</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -1705,38 +1708,38 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" t="n">
         <v>4064</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
         <v>3926</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -1751,12 +1754,12 @@
         <v>3893</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -1765,38 +1768,38 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
         <v>3606</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" t="n">
         <v>3570</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
@@ -1805,18 +1808,18 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
         <v>3368</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
@@ -1825,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
         <v>3015</v>
@@ -1842,7 +1845,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -1851,32 +1854,32 @@
         <v>2852</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E32" t="n">
         <v>1725</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
@@ -1885,38 +1888,38 @@
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" t="n">
         <v>1529</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E34" t="n">
         <v>1280</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -1925,18 +1928,18 @@
         <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" t="n">
         <v>870</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -1945,13 +1948,13 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E36" t="n">
         <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2037,10 +2040,10 @@
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2048,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -2057,16 +2060,16 @@
         <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -2074,7 +2077,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
@@ -2083,16 +2086,16 @@
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -2126,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -2135,16 +2138,16 @@
         <v>377</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -2152,7 +2155,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
@@ -2161,16 +2164,16 @@
         <v>552</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -2178,7 +2181,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
@@ -2187,16 +2190,16 @@
         <v>728</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -2204,7 +2207,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -2213,16 +2216,16 @@
         <v>818</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -2230,7 +2233,7 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
@@ -2239,16 +2242,16 @@
         <v>870</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -2256,7 +2259,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -2265,16 +2268,16 @@
         <v>957</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2334,7 +2337,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
@@ -2343,16 +2346,16 @@
         <v>1024</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -2402,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
@@ -2411,13 +2414,13 @@
         <v>1151</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H18" t="s">
         <v>40</v>
@@ -2428,7 +2431,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -2437,16 +2440,16 @@
         <v>1278</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2454,7 +2457,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -2463,16 +2466,16 @@
         <v>1286</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2480,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
@@ -2489,16 +2492,16 @@
         <v>1392</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -2506,7 +2509,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -2515,16 +2518,16 @@
         <v>1419</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
@@ -2532,7 +2535,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
@@ -2541,16 +2544,16 @@
         <v>1514</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -2558,7 +2561,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
@@ -2567,16 +2570,16 @@
         <v>1529</v>
       </c>
       <c r="E24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25">
@@ -2584,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
         <v>25</v>
@@ -2628,7 +2631,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
@@ -2637,16 +2640,16 @@
         <v>1723</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -2654,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
@@ -2663,16 +2666,16 @@
         <v>1792</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -2712,7 +2715,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
@@ -2721,16 +2724,16 @@
         <v>1847</v>
       </c>
       <c r="E31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -2738,7 +2741,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
@@ -2747,13 +2750,13 @@
         <v>1883</v>
       </c>
       <c r="E32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H32" t="s">
         <v>40</v>
@@ -2764,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
         <v>25</v>
@@ -2773,16 +2776,16 @@
         <v>2055</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -2790,7 +2793,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
         <v>30</v>
@@ -2799,16 +2802,16 @@
         <v>2424</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
@@ -2831,10 +2834,10 @@
         <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -2842,7 +2845,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
@@ -2851,16 +2854,16 @@
         <v>2776</v>
       </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
@@ -2868,7 +2871,7 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
@@ -2877,16 +2880,16 @@
         <v>2902</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
@@ -2894,7 +2897,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
@@ -2903,13 +2906,13 @@
         <v>3015</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H38" t="s">
         <v>40</v>
@@ -2920,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>30</v>
@@ -2929,16 +2932,16 @@
         <v>3104</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -2946,7 +2949,7 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>25</v>
@@ -2955,16 +2958,16 @@
         <v>3214</v>
       </c>
       <c r="E40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
@@ -2972,7 +2975,7 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
@@ -2981,16 +2984,16 @@
         <v>3230</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>
       </c>
       <c r="H41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
@@ -2998,7 +3001,7 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
         <v>25</v>
@@ -3007,16 +3010,16 @@
         <v>3246</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -3024,7 +3027,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
@@ -3033,16 +3036,16 @@
         <v>3269</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -3050,7 +3053,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
@@ -3059,16 +3062,16 @@
         <v>3337</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45">
@@ -3076,7 +3079,7 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
@@ -3085,16 +3088,16 @@
         <v>3368</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
@@ -3102,7 +3105,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
@@ -3111,16 +3114,16 @@
         <v>3469</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
         <v>33</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47">
@@ -3128,7 +3131,7 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
@@ -3137,16 +3140,16 @@
         <v>3606</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48">
@@ -3154,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -3163,16 +3166,16 @@
         <v>3655</v>
       </c>
       <c r="E48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
@@ -3180,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
         <v>30</v>
@@ -3189,16 +3192,16 @@
         <v>3877</v>
       </c>
       <c r="E49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G49" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
@@ -3206,7 +3209,7 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
         <v>30</v>
@@ -3215,16 +3218,16 @@
         <v>3881</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51">
@@ -3232,7 +3235,7 @@
         <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
         <v>36</v>
@@ -3241,16 +3244,16 @@
         <v>3893</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F51" t="s">
         <v>33</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52">
@@ -3258,7 +3261,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
@@ -3267,16 +3270,16 @@
         <v>4047</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53">
@@ -3284,7 +3287,7 @@
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
         <v>30</v>
@@ -3293,16 +3296,16 @@
         <v>4064</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54">
@@ -3310,7 +3313,7 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
         <v>30</v>
@@ -3319,13 +3322,13 @@
         <v>4418</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s">
         <v>33</v>
       </c>
       <c r="G54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H54" t="s">
         <v>40</v>
@@ -3336,7 +3339,7 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
         <v>30</v>
@@ -3345,16 +3348,16 @@
         <v>4530</v>
       </c>
       <c r="E55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F55" t="s">
         <v>22</v>
       </c>
       <c r="G55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56">
@@ -3362,7 +3365,7 @@
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C56" t="s">
         <v>30</v>
@@ -3371,16 +3374,16 @@
         <v>4547</v>
       </c>
       <c r="E56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -3440,7 +3443,7 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
         <v>20</v>
@@ -3449,16 +3452,16 @@
         <v>4900</v>
       </c>
       <c r="E59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
       </c>
       <c r="G59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60">
@@ -3466,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
         <v>30</v>
@@ -3484,7 +3487,7 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -3493,16 +3496,16 @@
         <v>5444</v>
       </c>
       <c r="E61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
@@ -3536,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
@@ -3545,16 +3548,16 @@
         <v>5604</v>
       </c>
       <c r="E63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
@@ -3588,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
         <v>30</v>
@@ -3597,13 +3600,13 @@
         <v>6461</v>
       </c>
       <c r="E65" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" t="s">
         <v>29</v>
@@ -3640,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C67" t="s">
         <v>30</v>
@@ -3649,16 +3652,16 @@
         <v>6830</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -3692,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
         <v>20</v>
@@ -3701,16 +3704,16 @@
         <v>6867</v>
       </c>
       <c r="E69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70">
@@ -3718,7 +3721,7 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
         <v>30</v>
@@ -3727,16 +3730,16 @@
         <v>7137</v>
       </c>
       <c r="E70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -51,6 +51,9 @@
     <t xml:space="preserve">Jackson</t>
   </si>
   <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
     <t xml:space="preserve">authorship</t>
   </si>
   <si>
@@ -126,15 +129,15 @@
     <t xml:space="preserve">3/31/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
     <t xml:space="preserve">24-872</t>
   </si>
   <si>
     <t xml:space="preserve">Hamm</t>
   </si>
   <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">12/10/2025</t>
   </si>
   <si>
@@ -237,9 +240,6 @@
     <t xml:space="preserve">Roberts; Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1/14/2026</t>
   </si>
   <si>
@@ -258,7 +258,7 @@
     <t xml:space="preserve">2/25/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Elingburg</t>
+    <t xml:space="preserve">Ellingburg</t>
   </si>
   <si>
     <t xml:space="preserve">Kavanaugh; Thomas</t>
@@ -904,6 +904,14 @@
         <v>3736</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -917,28 +925,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -946,25 +954,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>17030</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -972,25 +980,25 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>14065</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -998,25 +1006,25 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>13905</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1024,25 +1032,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
         <v>10237</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1050,25 +1058,25 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>9047</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1084,39 +1092,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
@@ -1125,39 +1133,39 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1165,51 +1173,51 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
         <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -1217,25 +1225,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>315</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1251,62 +1259,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
         <v>44972</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
         <v>24457</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1317,110 +1325,110 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
         <v>17710</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
         <v>16958</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
         <v>15423</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
         <v>9430</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>7928</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>7868</v>
@@ -1440,13 +1448,13 @@
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
         <v>7452</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -1460,7 +1468,7 @@
         <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
         <v>7218</v>
@@ -1480,13 +1488,13 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
         <v>6882</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1500,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
         <v>6830</v>
@@ -1534,7 +1542,7 @@
         <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>6695</v>
@@ -1554,13 +1562,13 @@
         <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" t="n">
         <v>6515</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1574,13 +1582,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
         <v>6461</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -1591,10 +1599,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" t="n">
         <v>6431</v>
@@ -1614,7 +1622,7 @@
         <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
         <v>5440</v>
@@ -1668,7 +1676,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
         <v>4547</v>
@@ -1688,7 +1696,7 @@
         <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>4426</v>
@@ -1708,13 +1716,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
         <v>4064</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
@@ -1728,13 +1736,13 @@
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
         <v>3926</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
@@ -1745,10 +1753,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
         <v>3893</v>
@@ -1768,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
         <v>3606</v>
@@ -1788,7 +1796,7 @@
         <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
         <v>3570</v>
@@ -1808,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
         <v>3368</v>
@@ -1828,18 +1836,18 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
         <v>3015</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
         <v>2</v>
@@ -1848,18 +1856,18 @@
         <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E31" t="n">
         <v>2852</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32" t="n">
         <v>2</v>
@@ -1868,13 +1876,13 @@
         <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
         <v>1725</v>
       </c>
       <c r="F32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -1885,10 +1893,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
         <v>1529</v>
@@ -1908,7 +1916,7 @@
         <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E34" t="n">
         <v>1280</v>
@@ -1925,10 +1933,10 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E35" t="n">
         <v>870</v>
@@ -1939,22 +1947,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E36" t="n">
         <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1970,39 +1978,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
@@ -2011,39 +2019,39 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -2051,51 +2059,51 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
         <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -2103,25 +2111,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>315</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -2132,7 +2140,7 @@
         <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>377</v>
@@ -2141,7 +2149,7 @@
         <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
         <v>122</v>
@@ -2152,13 +2160,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>552</v>
@@ -2167,10 +2175,10 @@
         <v>118</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
         <v>119</v>
@@ -2178,13 +2186,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>728</v>
@@ -2193,10 +2201,10 @@
         <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
         <v>119</v>
@@ -2210,7 +2218,7 @@
         <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
         <v>818</v>
@@ -2219,10 +2227,10 @@
         <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
@@ -2230,13 +2238,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>870</v>
@@ -2245,10 +2253,10 @@
         <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
         <v>117</v>
@@ -2262,7 +2270,7 @@
         <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>957</v>
@@ -2271,7 +2279,7 @@
         <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
         <v>127</v>
@@ -2285,25 +2293,25 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
         <v>975</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -2311,25 +2319,25 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
         <v>1009</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -2340,7 +2348,7 @@
         <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>1024</v>
@@ -2349,13 +2357,13 @@
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -2363,25 +2371,25 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
         <v>1049</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2390,7 +2398,7 @@
       </c>
       <c r="B17"/>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
         <v>1081</v>
@@ -2408,7 +2416,7 @@
         <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>1151</v>
@@ -2417,13 +2425,13 @@
         <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
         <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -2434,7 +2442,7 @@
         <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>1278</v>
@@ -2443,13 +2451,13 @@
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" t="s">
         <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -2460,7 +2468,7 @@
         <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>1286</v>
@@ -2469,7 +2477,7 @@
         <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" t="s">
         <v>134</v>
@@ -2486,7 +2494,7 @@
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>1392</v>
@@ -2495,10 +2503,10 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
         <v>74</v>
@@ -2512,22 +2520,22 @@
         <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
         <v>1419</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -2535,36 +2543,36 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
         <v>1514</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
         <v>1529</v>
@@ -2573,10 +2581,10 @@
         <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" t="s">
         <v>117</v>
@@ -2590,7 +2598,7 @@
         <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
         <v>1651</v>
@@ -2605,25 +2613,25 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>1691</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -2634,7 +2642,7 @@
         <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
         <v>1723</v>
@@ -2643,7 +2651,7 @@
         <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s">
         <v>83</v>
@@ -2660,7 +2668,7 @@
         <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
         <v>1792</v>
@@ -2680,11 +2688,11 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B29"/>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>1824</v>
@@ -2700,7 +2708,7 @@
       </c>
       <c r="B30"/>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" t="n">
         <v>1840</v>
@@ -2718,7 +2726,7 @@
         <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" t="n">
         <v>1847</v>
@@ -2727,7 +2735,7 @@
         <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G31" t="s">
         <v>83</v>
@@ -2744,7 +2752,7 @@
         <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
         <v>1883</v>
@@ -2753,13 +2761,13 @@
         <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
         <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -2770,7 +2778,7 @@
         <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
         <v>2055</v>
@@ -2779,7 +2787,7 @@
         <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
         <v>134</v>
@@ -2796,16 +2804,16 @@
         <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D34" t="n">
         <v>2424</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
         <v>142</v>
@@ -2816,28 +2824,28 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
         <v>2643</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -2848,7 +2856,7 @@
         <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
         <v>2776</v>
@@ -2857,7 +2865,7 @@
         <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -2874,7 +2882,7 @@
         <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D37" t="n">
         <v>2902</v>
@@ -2883,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -2900,7 +2908,7 @@
         <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D38" t="n">
         <v>3015</v>
@@ -2909,13 +2917,13 @@
         <v>113</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -2926,7 +2934,7 @@
         <v>121</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39" t="n">
         <v>3104</v>
@@ -2935,7 +2943,7 @@
         <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G39" t="s">
         <v>122</v>
@@ -2952,7 +2960,7 @@
         <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
         <v>3214</v>
@@ -2961,7 +2969,7 @@
         <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G40" t="s">
         <v>122</v>
@@ -2978,7 +2986,7 @@
         <v>124</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D41" t="n">
         <v>3230</v>
@@ -2987,10 +2995,10 @@
         <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H41" t="s">
         <v>74</v>
@@ -3004,7 +3012,7 @@
         <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
         <v>3246</v>
@@ -3013,13 +3021,13 @@
         <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G42" t="s">
         <v>134</v>
       </c>
       <c r="H42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
@@ -3030,7 +3038,7 @@
         <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
         <v>3269</v>
@@ -3039,13 +3047,13 @@
         <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G43" t="s">
         <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -3056,7 +3064,7 @@
         <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44" t="n">
         <v>3337</v>
@@ -3082,7 +3090,7 @@
         <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
         <v>3368</v>
@@ -3091,7 +3099,7 @@
         <v>112</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" t="s">
         <v>144</v>
@@ -3108,7 +3116,7 @@
         <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D46" t="n">
         <v>3469</v>
@@ -3117,7 +3125,7 @@
         <v>101</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G46" t="s">
         <v>127</v>
@@ -3134,7 +3142,7 @@
         <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D47" t="n">
         <v>3606</v>
@@ -3143,7 +3151,7 @@
         <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G47" t="s">
         <v>149</v>
@@ -3160,7 +3168,7 @@
         <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
         <v>3655</v>
@@ -3169,7 +3177,7 @@
         <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G48" t="s">
         <v>144</v>
@@ -3186,7 +3194,7 @@
         <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" t="n">
         <v>3877</v>
@@ -3195,7 +3203,7 @@
         <v>77</v>
       </c>
       <c r="F49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G49" t="s">
         <v>134</v>
@@ -3212,33 +3220,33 @@
         <v>150</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D50" t="n">
         <v>3881</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G50" t="s">
         <v>142</v>
       </c>
       <c r="H50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
         <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>3893</v>
@@ -3247,10 +3255,10 @@
         <v>106</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H51" t="s">
         <v>107</v>
@@ -3264,22 +3272,22 @@
         <v>150</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52" t="n">
         <v>4047</v>
       </c>
       <c r="E52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F52" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G52" t="s">
         <v>142</v>
       </c>
       <c r="H52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
@@ -3290,7 +3298,7 @@
         <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" t="n">
         <v>4064</v>
@@ -3299,13 +3307,13 @@
         <v>103</v>
       </c>
       <c r="F53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G53" t="s">
         <v>153</v>
       </c>
       <c r="H53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
@@ -3316,7 +3324,7 @@
         <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D54" t="n">
         <v>4418</v>
@@ -3325,13 +3333,13 @@
         <v>75</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" t="s">
         <v>130</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -3342,22 +3350,22 @@
         <v>154</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" t="n">
         <v>4530</v>
       </c>
       <c r="E55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G55" t="s">
         <v>127</v>
       </c>
       <c r="H55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
@@ -3368,7 +3376,7 @@
         <v>155</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
         <v>4547</v>
@@ -3377,7 +3385,7 @@
         <v>99</v>
       </c>
       <c r="F56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G56" t="s">
         <v>156</v>
@@ -3391,25 +3399,25 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D57" t="n">
         <v>4718</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
@@ -3420,7 +3428,7 @@
         <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D58" t="n">
         <v>4748</v>
@@ -3429,13 +3437,13 @@
         <v>38</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
@@ -3446,22 +3454,22 @@
         <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59" t="n">
         <v>4900</v>
       </c>
       <c r="E59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G59" t="s">
         <v>127</v>
       </c>
       <c r="H59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
@@ -3472,7 +3480,7 @@
         <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D60" t="n">
         <v>5139</v>
@@ -3490,16 +3498,16 @@
         <v>141</v>
       </c>
       <c r="C61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D61" t="n">
         <v>5444</v>
       </c>
       <c r="E61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G61" t="s">
         <v>142</v>
@@ -3513,25 +3521,25 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D62" t="n">
         <v>5484</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -3542,7 +3550,7 @@
         <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" t="n">
         <v>5604</v>
@@ -3551,13 +3559,13 @@
         <v>80</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G63" t="s">
         <v>132</v>
       </c>
       <c r="H63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
@@ -3568,7 +3576,7 @@
         <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D64" t="n">
         <v>6232</v>
@@ -3577,13 +3585,13 @@
         <v>38</v>
       </c>
       <c r="F64" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G64" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -3594,7 +3602,7 @@
         <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D65" t="n">
         <v>6461</v>
@@ -3603,13 +3611,13 @@
         <v>89</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G65" t="s">
         <v>158</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -3620,7 +3628,7 @@
         <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D66" t="n">
         <v>6717</v>
@@ -3629,13 +3637,13 @@
         <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -3646,7 +3654,7 @@
         <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D67" t="n">
         <v>6830</v>
@@ -3655,7 +3663,7 @@
         <v>82</v>
       </c>
       <c r="F67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G67" t="s">
         <v>74</v>
@@ -3669,25 +3677,25 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
         <v>31</v>
-      </c>
-      <c r="C68" t="s">
-        <v>30</v>
       </c>
       <c r="D68" t="n">
         <v>6862</v>
       </c>
       <c r="E68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
@@ -3698,22 +3706,22 @@
         <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" t="n">
         <v>6867</v>
       </c>
       <c r="E69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G69" t="s">
         <v>132</v>
       </c>
       <c r="H69" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70">
@@ -3724,22 +3732,22 @@
         <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D70" t="n">
         <v>7137</v>
       </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G70" t="s">
         <v>132</v>
       </c>
       <c r="H70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71">
@@ -3747,25 +3755,25 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>9047</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72">
@@ -3773,25 +3781,25 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D72" t="n">
         <v>10237</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
@@ -3799,25 +3807,25 @@
         <v>6</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D73" t="n">
         <v>13905</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -3825,25 +3833,25 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D74" t="n">
         <v>14065</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
@@ -3851,25 +3859,25 @@
         <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D75" t="n">
         <v>17030</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -129,262 +129,262 @@
     <t xml:space="preserve">3/31/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">25-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3/23/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coney Island Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/25/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Gorsuch; Barrett; Kagan; Jackson; Thomas; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Thomas; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Sotomayor; Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Kagan; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor; Jackson; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hencely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/22/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/24/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/14/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Sotomayor; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Alito; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellingburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/25/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Sotomayor; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquemines Parish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/17/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Barrett; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/14/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enbridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/26/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urias-Orellana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAM Pension Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/24/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-872</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">12/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/21/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">3/23/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coney Island Auto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/8/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_opinions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Gorsuch; Barrett; Kagan; Jackson; Thomas; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Thomas; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Sotomayor; Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Kagan; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor; Jackson; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/9/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hencely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/22/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/24/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/14/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Havana Docks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Sotomayor; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarreal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Alito; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/25/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ellingburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/25/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Sotomayor; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaquemines Parish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/17/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Barrett; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/14/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enbridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hain Celestial Grp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/26/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montgomery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urias-Orellana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAM Pension Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/24/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R.W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/10/2025</t>
   </si>
   <si>
     <t xml:space="preserve">25-248</t>
@@ -1127,39 +1127,39 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
       </c>
       <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>211</v>
+      </c>
+      <c r="E3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="n">
-        <v>209</v>
-      </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
         <v>44</v>
@@ -1170,54 +1170,54 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
         <v>48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1225,25 +1225,25 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1259,19 +1259,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>55</v>
-      </c>
-      <c r="C1" t="s">
-        <v>56</v>
       </c>
       <c r="D1" t="s">
         <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
         <v>19</v>
@@ -1285,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -1328,13 +1328,13 @@
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>17710</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1359,33 +1359,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>15423</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1394,58 +1394,58 @@
         <v>9430</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>7928</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="E9" t="n">
         <v>7868</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
@@ -1454,52 +1454,52 @@
         <v>7452</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
         <v>7218</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
         <v>6882</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -1508,13 +1508,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E13" t="n">
         <v>6830</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -1523,7 +1523,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="n">
@@ -1533,7 +1533,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
@@ -1542,13 +1542,13 @@
         <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E15" t="n">
         <v>6695</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -1562,13 +1562,13 @@
         <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
         <v>6515</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1582,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
         <v>6461</v>
@@ -1599,10 +1599,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
         <v>6431</v>
@@ -1622,13 +1622,13 @@
         <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
         <v>5440</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1676,7 +1676,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
         <v>4547</v>
@@ -1716,13 +1716,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>4064</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -1736,13 +1736,13 @@
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
         <v>3926</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -1776,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
         <v>3606</v>
@@ -1796,7 +1796,7 @@
         <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
         <v>3570</v>
@@ -1816,13 +1816,13 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
         <v>3368</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
@@ -1836,18 +1836,18 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
         <v>3015</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B31" t="n">
         <v>2</v>
@@ -1862,12 +1862,12 @@
         <v>2852</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B32" t="n">
         <v>2</v>
@@ -1876,13 +1876,13 @@
         <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E32" t="n">
         <v>1725</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -1896,7 +1896,7 @@
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E33" t="n">
         <v>1529</v>
@@ -1916,7 +1916,7 @@
         <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="E34" t="n">
         <v>1280</v>
@@ -1936,7 +1936,7 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E35" t="n">
         <v>870</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -1956,13 +1956,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E36" t="n">
         <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2007,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -2016,16 +2016,16 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -2033,7 +2033,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -2042,16 +2042,16 @@
         <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -2068,16 +2068,16 @@
         <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -2094,16 +2094,16 @@
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
         <v>48</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -2137,7 +2137,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -2146,16 +2146,16 @@
         <v>377</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -2175,10 +2175,10 @@
         <v>118</v>
       </c>
       <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
       </c>
       <c r="H8" t="s">
         <v>119</v>
@@ -2201,10 +2201,10 @@
         <v>118</v>
       </c>
       <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
         <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
       </c>
       <c r="H9" t="s">
         <v>119</v>
@@ -2227,13 +2227,13 @@
         <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -2253,10 +2253,10 @@
         <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H11" t="s">
         <v>117</v>
@@ -2357,13 +2357,13 @@
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -2422,7 +2422,7 @@
         <v>1151</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -2431,7 +2431,7 @@
         <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -2448,16 +2448,16 @@
         <v>1278</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
         <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -2474,16 +2474,16 @@
         <v>1286</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
         <v>134</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
@@ -2503,13 +2503,13 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -2526,16 +2526,16 @@
         <v>1419</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
         <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -2543,7 +2543,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
         <v>31</v>
@@ -2552,16 +2552,16 @@
         <v>1514</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -2581,10 +2581,10 @@
         <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s">
         <v>117</v>
@@ -2651,10 +2651,10 @@
         <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
         <v>100</v>
@@ -2735,10 +2735,10 @@
         <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s">
         <v>100</v>
@@ -2758,7 +2758,7 @@
         <v>1883</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -2767,7 +2767,7 @@
         <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
@@ -2784,16 +2784,16 @@
         <v>2055</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G33" t="s">
         <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
@@ -2810,16 +2810,16 @@
         <v>2424</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
         <v>142</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
@@ -2827,7 +2827,7 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -2836,16 +2836,16 @@
         <v>2643</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -2865,7 +2865,7 @@
         <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -2891,13 +2891,13 @@
         <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -2917,13 +2917,13 @@
         <v>113</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G38" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
@@ -2931,7 +2931,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
@@ -2940,16 +2940,16 @@
         <v>3104</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F39" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G39" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="H39" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
@@ -2957,7 +2957,7 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
         <v>26</v>
@@ -2966,16 +2966,16 @@
         <v>3214</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="H40" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
@@ -2995,13 +2995,13 @@
         <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
         <v>29</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
@@ -3021,13 +3021,13 @@
         <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
         <v>134</v>
       </c>
       <c r="H42" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -3047,13 +3047,13 @@
         <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G43" t="s">
         <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -3099,13 +3099,13 @@
         <v>112</v>
       </c>
       <c r="F45" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
         <v>144</v>
       </c>
       <c r="H45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46">
@@ -3151,7 +3151,7 @@
         <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G47" t="s">
         <v>149</v>
@@ -3177,7 +3177,7 @@
         <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G48" t="s">
         <v>144</v>
@@ -3200,16 +3200,16 @@
         <v>3877</v>
       </c>
       <c r="E49" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G49" t="s">
         <v>134</v>
       </c>
       <c r="H49" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50">
@@ -3226,16 +3226,16 @@
         <v>3881</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G50" t="s">
         <v>142</v>
       </c>
       <c r="H50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
@@ -3258,7 +3258,7 @@
         <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H51" t="s">
         <v>107</v>
@@ -3278,16 +3278,16 @@
         <v>4047</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F52" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G52" t="s">
         <v>142</v>
       </c>
       <c r="H52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
@@ -3307,13 +3307,13 @@
         <v>103</v>
       </c>
       <c r="F53" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G53" t="s">
         <v>153</v>
       </c>
       <c r="H53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
@@ -3330,7 +3330,7 @@
         <v>4418</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -3339,7 +3339,7 @@
         <v>130</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
@@ -3356,7 +3356,7 @@
         <v>4530</v>
       </c>
       <c r="E55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F55" t="s">
         <v>23</v>
@@ -3365,7 +3365,7 @@
         <v>127</v>
       </c>
       <c r="H55" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
@@ -3385,7 +3385,7 @@
         <v>99</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G56" t="s">
         <v>156</v>
@@ -3425,7 +3425,7 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
         <v>21</v>
@@ -3434,16 +3434,16 @@
         <v>4748</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G58" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59">
@@ -3460,7 +3460,7 @@
         <v>4900</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
@@ -3469,7 +3469,7 @@
         <v>127</v>
       </c>
       <c r="H59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60">
@@ -3504,16 +3504,16 @@
         <v>5444</v>
       </c>
       <c r="E61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
         <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62">
@@ -3556,16 +3556,16 @@
         <v>5604</v>
       </c>
       <c r="E63" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G63" t="s">
         <v>132</v>
       </c>
       <c r="H63" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -3573,7 +3573,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
         <v>26</v>
@@ -3582,16 +3582,16 @@
         <v>6232</v>
       </c>
       <c r="E64" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G64" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H64" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -3611,7 +3611,7 @@
         <v>89</v>
       </c>
       <c r="F65" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G65" t="s">
         <v>158</v>
@@ -3625,7 +3625,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
@@ -3634,16 +3634,16 @@
         <v>6717</v>
       </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G66" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H66" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67">
@@ -3660,16 +3660,16 @@
         <v>6830</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68">
@@ -3712,16 +3712,16 @@
         <v>6867</v>
       </c>
       <c r="E69" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F69" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G69" t="s">
         <v>132</v>
       </c>
       <c r="H69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70">
@@ -3738,16 +3738,16 @@
         <v>7137</v>
       </c>
       <c r="E70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F70" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G70" t="s">
         <v>132</v>
       </c>
       <c r="H70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -78,361 +78,640 @@
     <t xml:space="preserve">date_decided</t>
   </si>
   <si>
+    <t xml:space="preserve">25-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dissent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/30/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-1287</t>
   </si>
   <si>
-    <t xml:space="preserve">Dissent</t>
-  </si>
-  <si>
     <t xml:space="preserve">Learning Resources</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">11/5/2025</t>
   </si>
   <si>
     <t xml:space="preserve">2/20/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/15/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/29/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/8/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/29/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
-    <t xml:space="preserve">24-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/15/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/29/2026</t>
+    <t xml:space="preserve">25-112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/27/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FS Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/3/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/18/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/25/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/23/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coney Island Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Jackson; Kavanaugh; Thomas; Alito; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Gorsuch; Barrett; Kagan; Jackson; Thomas; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Gorsuch; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Thomas; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Kavanaugh; Jackson; Thomas; Alito; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wolford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Kagan; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/25/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.P.J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas; Gorsuch; Sotomayor; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Otro Lado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Thomas; Sotomayor; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Jackson; Gorsuch; Alito; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Sotomayor; Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Kagan; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/31/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Gorsuch; Kavanaugh; Barrett; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor; Jackson; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsanto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMD Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor; Thomas; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin v. Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Sotomayor; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/28/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Kagan; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hencely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/22/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Thomas; Jackson; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutherford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exxon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/14/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/24/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas; Sotomayor; Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Alito; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Thomas; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellingburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sripetch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/4/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/25/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keathley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Thomas; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Sotomayor; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquemines Parish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/17/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitchford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/1/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/14/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enbridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/23/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/26/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urias-Orellana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McCarthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/22/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAM Pension Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abouammo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/20/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flowers Foods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/26/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/24/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">24-856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/28/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/13/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25A312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/2/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/23/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/6/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-482</t>
   </si>
   <si>
     <t xml:space="preserve">Majority Opinion</t>
   </si>
   <si>
-    <t xml:space="preserve">24-539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/7/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/31/2026</t>
+    <t xml:space="preserve">10/14/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1159</t>
   </si>
   <si>
     <t xml:space="preserve">25-297</t>
   </si>
   <si>
-    <t xml:space="preserve">Zorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">3/23/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coney Island Auto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/8/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/25/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_opinions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Gorsuch; Barrett; Kagan; Jackson; Thomas; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Thomas; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Sotomayor; Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/21/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Kagan; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor; Jackson; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/9/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hencely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/22/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/24/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/14/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Havana Docks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Sotomayor; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarreal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Alito; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ellingburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Thomas; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/25/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Sotomayor; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaquemines Parish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/17/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Barrett; Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/14/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enbridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hain Celestial Grp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/26/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montgomery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urias-Orellana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAM Pension Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam; Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/24/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R.W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/20/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/3/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/23/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/14/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/6/2025</t>
+    <t xml:space="preserve">25-5774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/24/2026</t>
   </si>
   <si>
     <t xml:space="preserve">24-5438</t>
   </si>
   <si>
-    <t xml:space="preserve">24-1159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-5774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-1238</t>
+    <t xml:space="preserve">25-5</t>
   </si>
   <si>
     <t xml:space="preserve">24-813</t>
@@ -441,27 +720,66 @@
     <t xml:space="preserve">1/12/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">25-406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/21/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-1083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-7351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/1/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-5146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/30/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-466</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-568</t>
   </si>
   <si>
     <t xml:space="preserve">10/8/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">24-171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/1/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">23-1209</t>
   </si>
   <si>
+    <t xml:space="preserve">25-748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-699</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-440</t>
   </si>
   <si>
+    <t xml:space="preserve">25-197</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-777</t>
   </si>
   <si>
+    <t xml:space="preserve">25-51</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-993</t>
   </si>
   <si>
@@ -471,7 +789,7 @@
     <t xml:space="preserve">24-351</t>
   </si>
   <si>
-    <t xml:space="preserve">25-51</t>
+    <t xml:space="preserve">24-889</t>
   </si>
   <si>
     <t xml:space="preserve">24-783</t>
@@ -483,16 +801,28 @@
     <t xml:space="preserve">24-924</t>
   </si>
   <si>
+    <t xml:space="preserve">24-820</t>
+  </si>
+  <si>
     <t xml:space="preserve">25-83</t>
   </si>
   <si>
-    <t xml:space="preserve">3/30/2026</t>
+    <t xml:space="preserve">23-1197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/9/2025</t>
   </si>
   <si>
     <t xml:space="preserve">24-781</t>
   </si>
   <si>
     <t xml:space="preserve">12/2/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-1260</t>
   </si>
   <si>
     <t xml:space="preserve">24-1021</t>
@@ -837,7 +1167,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3954</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="3">
@@ -845,7 +1175,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>3149</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +1183,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4118</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="5">
@@ -861,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3833</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="6">
@@ -869,7 +1199,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3788</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="7">
@@ -877,7 +1207,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>5742</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +1215,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>6677</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="9">
@@ -893,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>1793</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="10">
@@ -901,7 +1231,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3736</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +1239,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>1249</v>
+        <v>1580</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +1281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -960,7 +1290,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>17030</v>
+        <v>29354</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
@@ -977,28 +1307,28 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>14065</v>
+        <v>18979</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -1006,77 +1336,77 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>13905</v>
+        <v>16019</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>10237</v>
+        <v>15895</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>9047</v>
+        <v>14719</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1118,48 +1448,48 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>209</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
         <v>44</v>
@@ -1170,80 +1500,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>228</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1259,19 +1589,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
         <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
         <v>19</v>
@@ -1282,16 +1612,16 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>44972</v>
+        <v>60392</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -1299,162 +1629,162 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>24457</v>
+        <v>49995</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>17710</v>
+        <v>32601</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>16958</v>
+        <v>26687</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>15423</v>
+        <v>24599</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>9430</v>
+        <v>23261</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>7928</v>
+        <v>21877</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20755</v>
+      </c>
+      <c r="F9" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7868</v>
-      </c>
-      <c r="F9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>7452</v>
+        <v>20463</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -1462,507 +1792,1139 @@
         <v>79</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>7218</v>
+        <v>19563</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>6882</v>
+        <v>19215</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>6830</v>
+        <v>18392</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14"/>
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
       <c r="E14" t="n">
-        <v>6790</v>
-      </c>
-      <c r="F14"/>
+        <v>17999</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="E15" t="n">
-        <v>6695</v>
+        <v>14686</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>6515</v>
+        <v>14577</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>14506</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E18" t="n">
-        <v>6431</v>
+        <v>13990</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>5440</v>
+        <v>13874</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>5129</v>
+        <v>13229</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21"/>
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
       <c r="E21" t="n">
-        <v>4745</v>
-      </c>
-      <c r="F21"/>
+        <v>13196</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
-        <v>4547</v>
+        <v>12751</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>4426</v>
+        <v>11765</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>4064</v>
+        <v>10699</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>3926</v>
+        <v>10566</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E26" t="n">
-        <v>3893</v>
+        <v>10505</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>3606</v>
+        <v>9487</v>
       </c>
       <c r="F27" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="E28" t="n">
-        <v>3570</v>
+        <v>9462</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
-        <v>3368</v>
+        <v>8523</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>3015</v>
+        <v>8495</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
       </c>
       <c r="E31" t="n">
-        <v>2852</v>
+        <v>8298</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>1725</v>
+        <v>8026</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E33" t="n">
-        <v>1529</v>
+        <v>7817</v>
       </c>
       <c r="F33" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E34" t="n">
-        <v>1280</v>
+        <v>7719</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E35" t="n">
-        <v>870</v>
+        <v>7679</v>
       </c>
       <c r="F35" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7605</v>
+      </c>
+      <c r="F36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7462</v>
+      </c>
+      <c r="F37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7143</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7022</v>
+      </c>
+      <c r="F39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6626</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6553</v>
+      </c>
+      <c r="F41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6393</v>
+      </c>
+      <c r="F42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6086</v>
+      </c>
+      <c r="F43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5951</v>
+      </c>
+      <c r="F44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5439</v>
+      </c>
+      <c r="F45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5355</v>
+      </c>
+      <c r="F46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5268</v>
+      </c>
+      <c r="F47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>157</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4965</v>
+      </c>
+      <c r="F48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4709</v>
+      </c>
+      <c r="F49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4386</v>
+      </c>
+      <c r="F50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4352</v>
+      </c>
+      <c r="F51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4273</v>
+      </c>
+      <c r="F52" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4072</v>
+      </c>
+      <c r="F53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3908</v>
+      </c>
+      <c r="F54" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>11</v>
       </c>
-      <c r="D36" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3893</v>
+      </c>
+      <c r="F55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3831</v>
+      </c>
+      <c r="F56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3754</v>
+      </c>
+      <c r="F57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3203</v>
+      </c>
+      <c r="F58" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3139</v>
+      </c>
+      <c r="F59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F60" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2338</v>
+      </c>
+      <c r="F62" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F63" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>155</v>
+      </c>
+      <c r="D64" t="s">
+        <v>53</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>53</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1529</v>
+      </c>
+      <c r="F65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>53</v>
+      </c>
+      <c r="E66" t="n">
+        <v>870</v>
+      </c>
+      <c r="F66" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" t="n">
         <v>228</v>
       </c>
-      <c r="F36" t="s">
-        <v>48</v>
+      <c r="F67" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2969,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -2016,62 +2978,62 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
         <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="n">
-        <v>209</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -2082,80 +3044,80 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>228</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -2163,275 +3125,285 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>552</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="H8" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>728</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>194</v>
       </c>
       <c r="H9" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>818</v>
+        <v>271</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>870</v>
+        <v>315</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>957</v>
+        <v>354</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>975</v>
+        <v>377</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>1009</v>
+        <v>541</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>1024</v>
+        <v>618</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>1049</v>
+        <v>640</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17"/>
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>1081</v>
-      </c>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
+        <v>728</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>1151</v>
+        <v>728</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -2439,387 +3411,415 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>1278</v>
+        <v>739</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="H19" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>1286</v>
+        <v>748</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G20" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>1392</v>
+        <v>794</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="H21" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>1419</v>
+        <v>845</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>1514</v>
+        <v>870</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>1529</v>
+        <v>917</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D25" t="n">
-        <v>1651</v>
-      </c>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
+        <v>949</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D26" t="n">
-        <v>1691</v>
+        <v>955</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>1723</v>
+        <v>1007</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
-        <v>1792</v>
+        <v>1116</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29"/>
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>213</v>
+      </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D29" t="n">
-        <v>1824</v>
-      </c>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
+        <v>1124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
         <v>6</v>
       </c>
-      <c r="B30"/>
+      <c r="B30" t="s">
+        <v>214</v>
+      </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D30" t="n">
-        <v>1840</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
+        <v>1139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D31" t="n">
-        <v>1847</v>
+        <v>1140</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>1883</v>
+        <v>1193</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="H32" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D33" t="n">
-        <v>2055</v>
+        <v>1200</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D34" t="n">
-        <v>2424</v>
+        <v>1201</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="H34" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -2827,363 +3827,363 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>2643</v>
+        <v>1214</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G35" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="H35" t="s">
-        <v>40</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D36" t="n">
-        <v>2776</v>
+        <v>1286</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D37" t="n">
-        <v>2902</v>
+        <v>1365</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>3015</v>
+        <v>1399</v>
       </c>
       <c r="E38" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="H38" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D39" t="n">
-        <v>3104</v>
+        <v>1400</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>223</v>
       </c>
       <c r="H39" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>3214</v>
+        <v>1529</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="H40" t="s">
-        <v>52</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D41" t="n">
-        <v>3230</v>
+        <v>1561</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="H41" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>3246</v>
+        <v>1630</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="H42" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1651</v>
+      </c>
+      <c r="E43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" t="n">
-        <v>3269</v>
-      </c>
-      <c r="E43" t="s">
-        <v>87</v>
-      </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G43" t="s">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D44" t="n">
-        <v>3337</v>
+        <v>1681</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="H44" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D45" t="n">
-        <v>3368</v>
+        <v>1723</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G45" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H45" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D46" t="n">
-        <v>3469</v>
+        <v>1727</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G46" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="H46" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D47" t="n">
-        <v>3606</v>
+        <v>1731</v>
       </c>
       <c r="E47" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G47" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="H47" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D48" t="n">
-        <v>3655</v>
+        <v>1741</v>
       </c>
       <c r="E48" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G48" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="H48" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -3191,51 +4191,51 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D49" t="n">
-        <v>3877</v>
+        <v>1794</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="H49" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D50" t="n">
-        <v>3881</v>
+        <v>1804</v>
       </c>
       <c r="E50" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G50" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51">
@@ -3243,103 +4243,103 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
       </c>
       <c r="D51" t="n">
-        <v>3893</v>
+        <v>1822</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="H51" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1837</v>
+      </c>
+      <c r="E52" t="s">
+        <v>149</v>
+      </c>
+      <c r="F52" t="s">
         <v>150</v>
       </c>
-      <c r="C52" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4047</v>
-      </c>
-      <c r="E52" t="s">
-        <v>70</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
       <c r="G52" t="s">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D53" t="n">
-        <v>4064</v>
+        <v>1894</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="H53" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D54" t="n">
-        <v>4418</v>
+        <v>1977</v>
       </c>
       <c r="E54" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G54" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="H54" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
@@ -3347,51 +4347,51 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D55" t="n">
-        <v>4530</v>
+        <v>1999</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G55" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="H55" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D56" t="n">
-        <v>4547</v>
+        <v>2031</v>
       </c>
       <c r="E56" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G56" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="H56" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57">
@@ -3399,25 +4399,25 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D57" t="n">
-        <v>4718</v>
+        <v>2055</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G57" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="H57" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58">
@@ -3425,458 +4425,2780 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>236</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D58" t="n">
-        <v>4748</v>
+        <v>2143</v>
       </c>
       <c r="E58" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F58" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G58" t="s">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="H58" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D59" t="n">
-        <v>4900</v>
+        <v>2151</v>
       </c>
       <c r="E59" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
       </c>
       <c r="G59" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="H59" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D60" t="n">
-        <v>5139</v>
-      </c>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
+        <v>2338</v>
+      </c>
+      <c r="E60" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" t="s">
+        <v>142</v>
+      </c>
+      <c r="H60" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D61" t="n">
-        <v>5444</v>
+        <v>2402</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G61" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="H61" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D62" t="n">
-        <v>5484</v>
+        <v>2412</v>
       </c>
       <c r="E62" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G62" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D63" t="n">
-        <v>5604</v>
+        <v>2516</v>
       </c>
       <c r="E63" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G63" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="H63" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>228</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="D64" t="n">
-        <v>6232</v>
+        <v>2618</v>
       </c>
       <c r="E64" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G64" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="H64" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
-        <v>6461</v>
+        <v>2643</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="F65" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="D66" t="n">
-        <v>6717</v>
+        <v>2704</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G66" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H66" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D67" t="n">
-        <v>6830</v>
+        <v>2831</v>
       </c>
       <c r="E67" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="H67" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D68" t="n">
-        <v>6862</v>
+        <v>2832</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>242</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="D69" t="n">
-        <v>6867</v>
+        <v>2850</v>
       </c>
       <c r="E69" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G69" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="H69" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D70" t="n">
-        <v>7137</v>
+        <v>2943</v>
       </c>
       <c r="E70" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="F70" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D71" t="n">
-        <v>9047</v>
+        <v>2998</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="F71" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="H71" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D72" t="n">
-        <v>10237</v>
+        <v>3005</v>
       </c>
       <c r="E72" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>29</v>
+        <v>246</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>247</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="D73" t="n">
-        <v>13905</v>
+        <v>3139</v>
       </c>
       <c r="E73" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G73" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>14065</v>
+        <v>3203</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="C75" t="s">
         <v>21</v>
       </c>
       <c r="D75" t="n">
-        <v>17030</v>
+        <v>3243</v>
       </c>
       <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" t="s">
+        <v>217</v>
+      </c>
+      <c r="H75" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C76" t="s">
+        <v>222</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3262</v>
+      </c>
+      <c r="E76" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" t="s">
+        <v>53</v>
+      </c>
+      <c r="G76" t="s">
+        <v>58</v>
+      </c>
+      <c r="H76" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>210</v>
+      </c>
+      <c r="C77" t="s">
+        <v>222</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3315</v>
+      </c>
+      <c r="E77" t="s">
+        <v>147</v>
+      </c>
+      <c r="F77" t="s">
+        <v>53</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E78" t="s">
+        <v>131</v>
+      </c>
+      <c r="F78" t="s">
+        <v>53</v>
+      </c>
+      <c r="G78" t="s">
+        <v>199</v>
+      </c>
+      <c r="H78" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" t="s">
+        <v>250</v>
+      </c>
+      <c r="C79" t="s">
+        <v>222</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3523</v>
+      </c>
+      <c r="E79" t="s">
+        <v>126</v>
+      </c>
+      <c r="F79" t="s">
+        <v>53</v>
+      </c>
+      <c r="G79" t="s">
+        <v>219</v>
+      </c>
+      <c r="H79" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>251</v>
+      </c>
+      <c r="C80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3569</v>
+      </c>
+      <c r="E80" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" t="s">
+        <v>181</v>
+      </c>
+      <c r="H80" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>232</v>
+      </c>
+      <c r="C81" t="s">
+        <v>222</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3602</v>
+      </c>
+      <c r="E81" t="s">
+        <v>149</v>
+      </c>
+      <c r="F81" t="s">
+        <v>150</v>
+      </c>
+      <c r="G81" t="s">
+        <v>233</v>
+      </c>
+      <c r="H81" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>211</v>
+      </c>
+      <c r="C82" t="s">
+        <v>222</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3702</v>
+      </c>
+      <c r="E82" t="s">
+        <v>159</v>
+      </c>
+      <c r="F82" t="s">
+        <v>48</v>
+      </c>
+      <c r="G82" t="s">
+        <v>212</v>
+      </c>
+      <c r="H82" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>240</v>
+      </c>
+      <c r="C83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3722</v>
+      </c>
+      <c r="E83" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" t="s">
+        <v>53</v>
+      </c>
+      <c r="G83" t="s">
+        <v>241</v>
+      </c>
+      <c r="H83" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" t="s">
+        <v>222</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3811</v>
+      </c>
+      <c r="E84" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84" t="s">
+        <v>54</v>
+      </c>
+      <c r="H84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" t="s">
+        <v>222</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3831</v>
+      </c>
+      <c r="E85" t="s">
+        <v>172</v>
+      </c>
+      <c r="F85" t="s">
+        <v>53</v>
+      </c>
+      <c r="G85" t="s">
+        <v>241</v>
+      </c>
+      <c r="H85" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" t="s">
+        <v>198</v>
+      </c>
+      <c r="C86" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3833</v>
+      </c>
+      <c r="E86" t="s">
+        <v>131</v>
+      </c>
+      <c r="F86" t="s">
+        <v>53</v>
+      </c>
+      <c r="G86" t="s">
+        <v>199</v>
+      </c>
+      <c r="H86" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>220</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3869</v>
+      </c>
+      <c r="E87" t="s">
+        <v>154</v>
+      </c>
+      <c r="F87" t="s">
+        <v>91</v>
+      </c>
+      <c r="G87" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" t="s">
+        <v>253</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3893</v>
+      </c>
+      <c r="E88" t="s">
+        <v>170</v>
+      </c>
+      <c r="F88" t="s">
+        <v>48</v>
+      </c>
+      <c r="G88" t="s">
+        <v>192</v>
+      </c>
+      <c r="H88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" t="s">
+        <v>254</v>
+      </c>
+      <c r="C89" t="s">
+        <v>222</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3908</v>
+      </c>
+      <c r="E89" t="s">
+        <v>168</v>
+      </c>
+      <c r="F89" t="s">
+        <v>53</v>
+      </c>
+      <c r="G89" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" t="s">
+        <v>256</v>
+      </c>
+      <c r="C90" t="s">
+        <v>222</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3958</v>
+      </c>
+      <c r="E90" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" t="s">
+        <v>246</v>
+      </c>
+      <c r="H90" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>244</v>
+      </c>
+      <c r="C91" t="s">
+        <v>222</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4024</v>
+      </c>
+      <c r="E91" t="s">
+        <v>137</v>
+      </c>
+      <c r="F91" t="s">
+        <v>53</v>
+      </c>
+      <c r="G91" t="s">
+        <v>181</v>
+      </c>
+      <c r="H91" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" t="s">
+        <v>257</v>
+      </c>
+      <c r="C92" t="s">
+        <v>222</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4072</v>
+      </c>
+      <c r="E92" t="s">
+        <v>167</v>
+      </c>
+      <c r="F92" t="s">
+        <v>53</v>
+      </c>
+      <c r="G92" t="s">
+        <v>33</v>
+      </c>
+      <c r="H92" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" t="s">
+        <v>236</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4208</v>
+      </c>
+      <c r="E93" t="s">
+        <v>102</v>
+      </c>
+      <c r="F93" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>10</v>
+      </c>
+      <c r="B94" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" t="s">
+        <v>38</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4294</v>
+      </c>
+      <c r="E94" t="s">
+        <v>126</v>
+      </c>
+      <c r="F94" t="s">
+        <v>53</v>
+      </c>
+      <c r="G94" t="s">
+        <v>219</v>
+      </c>
+      <c r="H94" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B95" t="s">
+        <v>218</v>
+      </c>
+      <c r="C95" t="s">
+        <v>222</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4338</v>
+      </c>
+      <c r="E95" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" t="s">
+        <v>53</v>
+      </c>
+      <c r="G95" t="s">
+        <v>219</v>
+      </c>
+      <c r="H95" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" t="n">
+        <v>4352</v>
+      </c>
+      <c r="E96" t="s">
+        <v>163</v>
+      </c>
+      <c r="F96" t="s">
+        <v>53</v>
+      </c>
+      <c r="G96" t="s">
+        <v>259</v>
+      </c>
+      <c r="H96" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" t="s">
+        <v>46</v>
+      </c>
+      <c r="C97" t="s">
+        <v>222</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4368</v>
+      </c>
+      <c r="E97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" t="s">
+        <v>48</v>
+      </c>
+      <c r="G97" t="s">
+        <v>49</v>
+      </c>
+      <c r="H97" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" t="s">
+        <v>234</v>
+      </c>
+      <c r="C98" t="s">
+        <v>222</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4394</v>
+      </c>
+      <c r="E98" t="s">
+        <v>143</v>
+      </c>
+      <c r="F98" t="s">
+        <v>48</v>
+      </c>
+      <c r="G98" t="s">
+        <v>235</v>
+      </c>
+      <c r="H98" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" t="s">
+        <v>251</v>
+      </c>
+      <c r="C99" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4398</v>
+      </c>
+      <c r="E99" t="s">
+        <v>98</v>
+      </c>
+      <c r="F99" t="s">
+        <v>70</v>
+      </c>
+      <c r="G99" t="s">
+        <v>181</v>
+      </c>
+      <c r="H99" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4402</v>
+      </c>
+      <c r="E100" t="s">
+        <v>100</v>
+      </c>
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" t="s">
+        <v>194</v>
+      </c>
+      <c r="H100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" t="s">
+        <v>222</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4403</v>
+      </c>
+      <c r="E101" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" t="s">
+        <v>44</v>
+      </c>
+      <c r="H101" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" t="s">
+        <v>195</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4446</v>
+      </c>
+      <c r="E102" t="s">
+        <v>71</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" t="s">
+        <v>59</v>
+      </c>
+      <c r="H102" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>256</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4537</v>
+      </c>
+      <c r="E103" t="s">
+        <v>119</v>
+      </c>
+      <c r="F103" t="s">
+        <v>70</v>
+      </c>
+      <c r="G103" t="s">
+        <v>246</v>
+      </c>
+      <c r="H103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" t="s">
+        <v>38</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4580</v>
+      </c>
+      <c r="E104" t="s">
+        <v>52</v>
+      </c>
+      <c r="F104" t="s">
+        <v>53</v>
+      </c>
+      <c r="G104" t="s">
+        <v>54</v>
+      </c>
+      <c r="H104" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" t="s">
+        <v>260</v>
+      </c>
+      <c r="C105" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4799</v>
+      </c>
+      <c r="E105" t="s">
+        <v>107</v>
+      </c>
+      <c r="F105" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" t="s">
+        <v>212</v>
+      </c>
+      <c r="H105" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B106" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" t="s">
+        <v>38</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E106" t="s">
+        <v>35</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" t="s">
+        <v>36</v>
+      </c>
+      <c r="H106" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4849</v>
+      </c>
+      <c r="E107" t="s">
+        <v>124</v>
+      </c>
+      <c r="F107" t="s">
+        <v>48</v>
+      </c>
+      <c r="G107" t="s">
+        <v>217</v>
+      </c>
+      <c r="H107" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" t="s">
+        <v>190</v>
+      </c>
+      <c r="C108" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4867</v>
+      </c>
+      <c r="E108" t="s">
+        <v>79</v>
+      </c>
+      <c r="F108" t="s">
+        <v>70</v>
+      </c>
+      <c r="G108" t="s">
+        <v>44</v>
+      </c>
+      <c r="H108" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" t="s">
+        <v>261</v>
+      </c>
+      <c r="C109" t="s">
+        <v>222</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4944</v>
+      </c>
+      <c r="E109" t="s">
+        <v>112</v>
+      </c>
+      <c r="F109" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" t="s">
+        <v>205</v>
+      </c>
+      <c r="H109" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>262</v>
+      </c>
+      <c r="C110" t="s">
+        <v>222</v>
+      </c>
+      <c r="D110" t="n">
+        <v>4965</v>
+      </c>
+      <c r="E110" t="s">
+        <v>157</v>
+      </c>
+      <c r="F110" t="s">
+        <v>53</v>
+      </c>
+      <c r="G110" t="s">
+        <v>243</v>
+      </c>
+      <c r="H110" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" t="n">
+        <v>5255</v>
+      </c>
+      <c r="E111" t="s">
+        <v>47</v>
+      </c>
+      <c r="F111" t="s">
+        <v>48</v>
+      </c>
+      <c r="G111" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112" t="s">
+        <v>204</v>
+      </c>
+      <c r="C112" t="s">
+        <v>222</v>
+      </c>
+      <c r="D112" t="n">
+        <v>5440</v>
+      </c>
+      <c r="E112" t="s">
+        <v>103</v>
+      </c>
+      <c r="F112" t="s">
+        <v>48</v>
+      </c>
+      <c r="G112" t="s">
+        <v>205</v>
+      </c>
+      <c r="H112" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>261</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="n">
+        <v>5561</v>
+      </c>
+      <c r="E113" t="s">
+        <v>112</v>
+      </c>
+      <c r="F113" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>205</v>
+      </c>
+      <c r="H113" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5572</v>
+      </c>
+      <c r="E114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" t="s">
+        <v>23</v>
+      </c>
+      <c r="G114" t="s">
+        <v>28</v>
+      </c>
+      <c r="H114" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>10</v>
+      </c>
+      <c r="B115" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" t="n">
+        <v>5594</v>
+      </c>
+      <c r="E115" t="s">
+        <v>122</v>
+      </c>
+      <c r="F115" t="s">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
+        <v>109</v>
+      </c>
+      <c r="H115" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" t="s">
+        <v>221</v>
+      </c>
+      <c r="C116" t="s">
+        <v>38</v>
+      </c>
+      <c r="D116" t="n">
+        <v>5743</v>
+      </c>
+      <c r="E116" t="s">
+        <v>135</v>
+      </c>
+      <c r="F116" t="s">
+        <v>53</v>
+      </c>
+      <c r="G116" t="s">
+        <v>223</v>
+      </c>
+      <c r="H116" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" t="s">
+        <v>222</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5749</v>
+      </c>
+      <c r="E117" t="s">
+        <v>92</v>
+      </c>
+      <c r="F117" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" t="s">
+        <v>199</v>
+      </c>
+      <c r="H117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" t="s">
+        <v>231</v>
+      </c>
+      <c r="C118" t="s">
+        <v>222</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5757</v>
+      </c>
+      <c r="E118" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" t="s">
+        <v>229</v>
+      </c>
+      <c r="H118" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" t="s">
+        <v>260</v>
+      </c>
+      <c r="C119" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5900</v>
+      </c>
+      <c r="E119" t="s">
+        <v>107</v>
+      </c>
+      <c r="F119" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" t="s">
+        <v>212</v>
+      </c>
+      <c r="H119" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>251</v>
+      </c>
+      <c r="C120" t="s">
+        <v>222</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5907</v>
+      </c>
+      <c r="E120" t="s">
+        <v>98</v>
+      </c>
+      <c r="F120" t="s">
+        <v>70</v>
+      </c>
+      <c r="G120" t="s">
+        <v>181</v>
+      </c>
+      <c r="H120" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>10</v>
+      </c>
+      <c r="B121" t="s">
+        <v>226</v>
+      </c>
+      <c r="C121" t="s">
+        <v>222</v>
+      </c>
+      <c r="D121" t="n">
+        <v>6068</v>
+      </c>
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" t="s">
+        <v>53</v>
+      </c>
+      <c r="G121" t="s">
+        <v>215</v>
+      </c>
+      <c r="H121" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" t="s">
+        <v>206</v>
+      </c>
+      <c r="C122" t="s">
+        <v>222</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6177</v>
+      </c>
+      <c r="E122" t="s">
+        <v>110</v>
+      </c>
+      <c r="F122" t="s">
+        <v>53</v>
+      </c>
+      <c r="G122" t="s">
+        <v>207</v>
+      </c>
+      <c r="H122" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>264</v>
+      </c>
+      <c r="C123" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6235</v>
+      </c>
+      <c r="E123" t="s">
+        <v>94</v>
+      </c>
+      <c r="F123" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" t="s">
+        <v>265</v>
+      </c>
+      <c r="H123" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" t="s">
+        <v>222</v>
+      </c>
+      <c r="D124" t="n">
+        <v>6244</v>
+      </c>
+      <c r="E124" t="s">
+        <v>114</v>
+      </c>
+      <c r="F124" t="s">
+        <v>23</v>
+      </c>
+      <c r="G124" t="s">
+        <v>217</v>
+      </c>
+      <c r="H124" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" t="s">
+        <v>39</v>
+      </c>
+      <c r="C125" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" t="n">
+        <v>6312</v>
+      </c>
+      <c r="E125" t="s">
+        <v>40</v>
+      </c>
+      <c r="F125" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" t="s">
+        <v>41</v>
+      </c>
+      <c r="H125" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>222</v>
+      </c>
+      <c r="D126" t="n">
+        <v>6318</v>
+      </c>
+      <c r="E126" t="s">
+        <v>27</v>
+      </c>
+      <c r="F126" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" t="s">
+        <v>28</v>
+      </c>
+      <c r="H126" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" t="s">
+        <v>209</v>
+      </c>
+      <c r="C127" t="s">
+        <v>222</v>
+      </c>
+      <c r="D127" t="n">
+        <v>6358</v>
+      </c>
+      <c r="E127" t="s">
+        <v>89</v>
+      </c>
+      <c r="F127" t="s">
+        <v>91</v>
+      </c>
+      <c r="G127" t="s">
+        <v>41</v>
+      </c>
+      <c r="H127" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B128" t="s">
+        <v>245</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="n">
+        <v>6457</v>
+      </c>
+      <c r="E128" t="s">
+        <v>115</v>
+      </c>
+      <c r="F128" t="s">
+        <v>91</v>
+      </c>
+      <c r="G128" t="s">
+        <v>246</v>
+      </c>
+      <c r="H128" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B129" t="s">
+        <v>204</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6563</v>
+      </c>
+      <c r="E129" t="s">
+        <v>103</v>
+      </c>
+      <c r="F129" t="s">
+        <v>48</v>
+      </c>
+      <c r="G129" t="s">
+        <v>205</v>
+      </c>
+      <c r="H129" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130" t="s">
+        <v>222</v>
+      </c>
+      <c r="D130" t="n">
+        <v>6626</v>
+      </c>
+      <c r="E130" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" t="s">
+        <v>53</v>
+      </c>
+      <c r="G130" t="s">
+        <v>267</v>
+      </c>
+      <c r="H130" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>10</v>
+      </c>
+      <c r="B131" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" t="s">
+        <v>38</v>
+      </c>
+      <c r="D131" t="n">
+        <v>6744</v>
+      </c>
+      <c r="E131" t="s">
         <v>22</v>
       </c>
-      <c r="F75" t="s">
-        <v>23</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="F131" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" t="s">
         <v>24</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H131" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>4</v>
+      </c>
+      <c r="B132" t="s">
+        <v>236</v>
+      </c>
+      <c r="C132" t="s">
+        <v>222</v>
+      </c>
+      <c r="D132" t="n">
+        <v>6845</v>
+      </c>
+      <c r="E132" t="s">
+        <v>102</v>
+      </c>
+      <c r="F132" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" t="s">
+        <v>33</v>
+      </c>
+      <c r="H132" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" t="s">
+        <v>190</v>
+      </c>
+      <c r="C133" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" t="n">
+        <v>6847</v>
+      </c>
+      <c r="E133" t="s">
+        <v>79</v>
+      </c>
+      <c r="F133" t="s">
+        <v>70</v>
+      </c>
+      <c r="G133" t="s">
+        <v>44</v>
+      </c>
+      <c r="H133" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>4</v>
+      </c>
+      <c r="B134" t="s">
+        <v>268</v>
+      </c>
+      <c r="C134" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" t="n">
+        <v>6921</v>
+      </c>
+      <c r="E134" t="s">
+        <v>96</v>
+      </c>
+      <c r="F134" t="s">
+        <v>70</v>
+      </c>
+      <c r="G134" t="s">
+        <v>166</v>
+      </c>
+      <c r="H134" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" t="s">
+        <v>268</v>
+      </c>
+      <c r="C135" t="s">
+        <v>222</v>
+      </c>
+      <c r="D135" t="n">
+        <v>7069</v>
+      </c>
+      <c r="E135" t="s">
+        <v>96</v>
+      </c>
+      <c r="F135" t="s">
+        <v>70</v>
+      </c>
+      <c r="G135" t="s">
+        <v>166</v>
+      </c>
+      <c r="H135" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" t="s">
+        <v>222</v>
+      </c>
+      <c r="D136" t="n">
+        <v>7113</v>
+      </c>
+      <c r="E136" t="s">
+        <v>82</v>
+      </c>
+      <c r="F136" t="s">
+        <v>48</v>
+      </c>
+      <c r="G136" t="s">
+        <v>215</v>
+      </c>
+      <c r="H136" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>10</v>
+      </c>
+      <c r="B137" t="s">
+        <v>42</v>
+      </c>
+      <c r="C137" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7244</v>
+      </c>
+      <c r="E137" t="s">
+        <v>43</v>
+      </c>
+      <c r="F137" t="s">
+        <v>23</v>
+      </c>
+      <c r="G137" t="s">
+        <v>44</v>
+      </c>
+      <c r="H137" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138" t="s">
+        <v>209</v>
+      </c>
+      <c r="C138" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" t="n">
+        <v>7411</v>
+      </c>
+      <c r="E138" t="s">
+        <v>89</v>
+      </c>
+      <c r="F138" t="s">
+        <v>91</v>
+      </c>
+      <c r="G138" t="s">
+        <v>41</v>
+      </c>
+      <c r="H138" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>269</v>
+      </c>
+      <c r="C139" t="s">
+        <v>222</v>
+      </c>
+      <c r="D139" t="n">
+        <v>7462</v>
+      </c>
+      <c r="E139" t="s">
+        <v>133</v>
+      </c>
+      <c r="F139" t="s">
+        <v>53</v>
+      </c>
+      <c r="G139" t="s">
+        <v>117</v>
+      </c>
+      <c r="H139" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>4</v>
+      </c>
+      <c r="B140" t="s">
+        <v>195</v>
+      </c>
+      <c r="C140" t="s">
+        <v>222</v>
+      </c>
+      <c r="D140" t="n">
+        <v>7785</v>
+      </c>
+      <c r="E140" t="s">
+        <v>71</v>
+      </c>
+      <c r="F140" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" t="s">
+        <v>59</v>
+      </c>
+      <c r="H140" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>4</v>
+      </c>
+      <c r="B141" t="s">
+        <v>190</v>
+      </c>
+      <c r="C141" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" t="n">
+        <v>7836</v>
+      </c>
+      <c r="E141" t="s">
+        <v>79</v>
+      </c>
+      <c r="F141" t="s">
+        <v>70</v>
+      </c>
+      <c r="G141" t="s">
+        <v>44</v>
+      </c>
+      <c r="H141" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>230</v>
+      </c>
+      <c r="C142" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" t="n">
+        <v>7987</v>
+      </c>
+      <c r="E142" t="s">
+        <v>86</v>
+      </c>
+      <c r="F142" t="s">
+        <v>70</v>
+      </c>
+      <c r="G142" t="s">
+        <v>223</v>
+      </c>
+      <c r="H142" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>3</v>
+      </c>
+      <c r="B143" t="s">
+        <v>46</v>
+      </c>
+      <c r="C143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" t="n">
+        <v>8101</v>
+      </c>
+      <c r="E143" t="s">
+        <v>47</v>
+      </c>
+      <c r="F143" t="s">
+        <v>48</v>
+      </c>
+      <c r="G143" t="s">
+        <v>49</v>
+      </c>
+      <c r="H143" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" t="s">
+        <v>264</v>
+      </c>
+      <c r="C144" t="s">
+        <v>222</v>
+      </c>
+      <c r="D144" t="n">
+        <v>8271</v>
+      </c>
+      <c r="E144" t="s">
+        <v>94</v>
+      </c>
+      <c r="F144" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" t="s">
+        <v>265</v>
+      </c>
+      <c r="H144" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" t="s">
+        <v>230</v>
+      </c>
+      <c r="C145" t="s">
+        <v>222</v>
+      </c>
+      <c r="D145" t="n">
+        <v>8281</v>
+      </c>
+      <c r="E145" t="s">
+        <v>86</v>
+      </c>
+      <c r="F145" t="s">
+        <v>70</v>
+      </c>
+      <c r="G145" t="s">
+        <v>223</v>
+      </c>
+      <c r="H145" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>2</v>
+      </c>
+      <c r="B146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" t="s">
+        <v>222</v>
+      </c>
+      <c r="D146" t="n">
+        <v>8329</v>
+      </c>
+      <c r="E146" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" t="s">
+        <v>24</v>
+      </c>
+      <c r="H146" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>196</v>
+      </c>
+      <c r="C147" t="s">
+        <v>222</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8445</v>
+      </c>
+      <c r="E147" t="s">
+        <v>74</v>
+      </c>
+      <c r="F147" t="s">
+        <v>23</v>
+      </c>
+      <c r="G147" t="s">
+        <v>197</v>
+      </c>
+      <c r="H147" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" t="s">
+        <v>193</v>
+      </c>
+      <c r="C148" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8596</v>
+      </c>
+      <c r="E148" t="s">
+        <v>100</v>
+      </c>
+      <c r="F148" t="s">
+        <v>23</v>
+      </c>
+      <c r="G148" t="s">
+        <v>194</v>
+      </c>
+      <c r="H148" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>202</v>
+      </c>
+      <c r="C149" t="s">
+        <v>222</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8771</v>
+      </c>
+      <c r="E149" t="s">
+        <v>68</v>
+      </c>
+      <c r="F149" t="s">
+        <v>70</v>
+      </c>
+      <c r="G149" t="s">
+        <v>203</v>
+      </c>
+      <c r="H149" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>10</v>
+      </c>
+      <c r="B150" t="s">
+        <v>263</v>
+      </c>
+      <c r="C150" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" t="n">
+        <v>8828</v>
+      </c>
+      <c r="E150" t="s">
+        <v>92</v>
+      </c>
+      <c r="F150" t="s">
+        <v>23</v>
+      </c>
+      <c r="G150" t="s">
+        <v>199</v>
+      </c>
+      <c r="H150" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151" t="s">
+        <v>222</v>
+      </c>
+      <c r="D151" t="n">
+        <v>10353</v>
+      </c>
+      <c r="E151" t="s">
+        <v>31</v>
+      </c>
+      <c r="F151" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" t="s">
+        <v>32</v>
+      </c>
+      <c r="H151" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>10</v>
+      </c>
+      <c r="B152" t="s">
+        <v>195</v>
+      </c>
+      <c r="C152" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" t="n">
+        <v>10759</v>
+      </c>
+      <c r="E152" t="s">
+        <v>71</v>
+      </c>
+      <c r="F152" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" t="s">
+        <v>59</v>
+      </c>
+      <c r="H152" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" t="s">
+        <v>39</v>
+      </c>
+      <c r="C153" t="s">
+        <v>222</v>
+      </c>
+      <c r="D153" t="n">
+        <v>10955</v>
+      </c>
+      <c r="E153" t="s">
+        <v>40</v>
+      </c>
+      <c r="F153" t="s">
+        <v>23</v>
+      </c>
+      <c r="G153" t="s">
+        <v>41</v>
+      </c>
+      <c r="H153" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>10</v>
+      </c>
+      <c r="B154" t="s">
+        <v>214</v>
+      </c>
+      <c r="C154" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" t="n">
+        <v>10963</v>
+      </c>
+      <c r="E154" t="s">
+        <v>82</v>
+      </c>
+      <c r="F154" t="s">
+        <v>48</v>
+      </c>
+      <c r="G154" t="s">
+        <v>215</v>
+      </c>
+      <c r="H154" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" t="s">
+        <v>196</v>
+      </c>
+      <c r="C155" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" t="n">
+        <v>11149</v>
+      </c>
+      <c r="E155" t="s">
+        <v>74</v>
+      </c>
+      <c r="F155" t="s">
+        <v>23</v>
+      </c>
+      <c r="G155" t="s">
+        <v>197</v>
+      </c>
+      <c r="H155" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B156" t="s">
+        <v>202</v>
+      </c>
+      <c r="C156" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" t="n">
+        <v>11214</v>
+      </c>
+      <c r="E156" t="s">
+        <v>68</v>
+      </c>
+      <c r="F156" t="s">
+        <v>70</v>
+      </c>
+      <c r="G156" t="s">
+        <v>203</v>
+      </c>
+      <c r="H156" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" t="s">
+        <v>231</v>
+      </c>
+      <c r="C157" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" t="n">
+        <v>11310</v>
+      </c>
+      <c r="E157" t="s">
+        <v>76</v>
+      </c>
+      <c r="F157" t="s">
+        <v>23</v>
+      </c>
+      <c r="G157" t="s">
+        <v>229</v>
+      </c>
+      <c r="H157" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>2</v>
+      </c>
+      <c r="B158" t="s">
+        <v>34</v>
+      </c>
+      <c r="C158" t="s">
+        <v>222</v>
+      </c>
+      <c r="D158" t="n">
+        <v>11906</v>
+      </c>
+      <c r="E158" t="s">
+        <v>35</v>
+      </c>
+      <c r="F158" t="s">
+        <v>23</v>
+      </c>
+      <c r="G158" t="s">
+        <v>36</v>
+      </c>
+      <c r="H158" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" t="n">
+        <v>12288</v>
+      </c>
+      <c r="E159" t="s">
+        <v>22</v>
+      </c>
+      <c r="F159" t="s">
+        <v>23</v>
+      </c>
+      <c r="G159" t="s">
+        <v>24</v>
+      </c>
+      <c r="H159" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>7</v>
+      </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" t="n">
+        <v>14719</v>
+      </c>
+      <c r="E160" t="s">
+        <v>27</v>
+      </c>
+      <c r="F160" t="s">
+        <v>23</v>
+      </c>
+      <c r="G160" t="s">
+        <v>28</v>
+      </c>
+      <c r="H160" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" t="s">
+        <v>34</v>
+      </c>
+      <c r="C161" t="s">
+        <v>21</v>
+      </c>
+      <c r="D161" t="n">
+        <v>15895</v>
+      </c>
+      <c r="E161" t="s">
+        <v>35</v>
+      </c>
+      <c r="F161" t="s">
+        <v>23</v>
+      </c>
+      <c r="G161" t="s">
+        <v>36</v>
+      </c>
+      <c r="H161" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" t="s">
+        <v>30</v>
+      </c>
+      <c r="C162" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" t="n">
+        <v>16019</v>
+      </c>
+      <c r="E162" t="s">
+        <v>31</v>
+      </c>
+      <c r="F162" t="s">
+        <v>23</v>
+      </c>
+      <c r="G162" t="s">
+        <v>32</v>
+      </c>
+      <c r="H162" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" t="n">
+        <v>18979</v>
+      </c>
+      <c r="E163" t="s">
+        <v>27</v>
+      </c>
+      <c r="F163" t="s">
+        <v>23</v>
+      </c>
+      <c r="G163" t="s">
+        <v>28</v>
+      </c>
+      <c r="H163" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>3</v>
+      </c>
+      <c r="B164" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" t="n">
+        <v>29354</v>
+      </c>
+      <c r="E164" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" t="s">
+        <v>23</v>
+      </c>
+      <c r="G164" t="s">
+        <v>24</v>
+      </c>
+      <c r="H164" t="s">
         <v>25</v>
       </c>
     </row>
